--- a/Docs/assets to import - final from logistic HQ.xlsx
+++ b/Docs/assets to import - final from logistic HQ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\logistic\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BC51184-FCAF-4E77-9412-461E0307961E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6FA2138-5EB1-4C48-BDB1-9EFAE872844E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-36" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Furniture" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8788" uniqueCount="493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9221" uniqueCount="495">
   <si>
     <t>Furniture</t>
   </si>
@@ -1517,6 +1517,12 @@
   </si>
   <si>
     <t>colored Printer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B&amp;Z </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owned By </t>
   </si>
 </sst>
 </file>
@@ -1571,7 +1577,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1594,12 +1600,6 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor rgb="FFFFFF00"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1631,7 +1631,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1682,7 +1682,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2017,22 +2016,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W300"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:X301"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.42578125" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.44140625" customWidth="1"/>
     <col min="7" max="7" width="23" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="63.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="23.109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="63.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -2102,8 +2101,11 @@
       <c r="W1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X1" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2170,8 +2172,11 @@
       <c r="V2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2238,8 +2243,11 @@
       <c r="V3" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X3" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2306,8 +2314,11 @@
       <c r="V4" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X4" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2374,8 +2385,11 @@
       <c r="V5" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X5" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2443,8 +2457,11 @@
         <v>29</v>
       </c>
       <c r="W6" s="2"/>
-    </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X6" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2511,8 +2528,11 @@
       <c r="V7" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X7" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2580,8 +2600,11 @@
         <v>29</v>
       </c>
       <c r="W8" s="2"/>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X8" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2649,8 +2672,11 @@
         <v>29</v>
       </c>
       <c r="W9" s="2"/>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X9" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2718,8 +2744,11 @@
         <v>29</v>
       </c>
       <c r="W10" s="2"/>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X10" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2787,8 +2816,11 @@
         <v>29</v>
       </c>
       <c r="W11" s="2"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X11" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2856,8 +2888,11 @@
         <v>29</v>
       </c>
       <c r="W12" s="2"/>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X12" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2925,8 +2960,11 @@
         <v>29</v>
       </c>
       <c r="W13" s="2"/>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X13" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2994,8 +3032,11 @@
         <v>29</v>
       </c>
       <c r="W14" s="2"/>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X14" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -3063,8 +3104,11 @@
         <v>29</v>
       </c>
       <c r="W15" s="2"/>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X15" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -3132,8 +3176,11 @@
         <v>29</v>
       </c>
       <c r="W16" s="2"/>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X16" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -3201,8 +3248,11 @@
         <v>29</v>
       </c>
       <c r="W17" s="2"/>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X17" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -3270,8 +3320,11 @@
         <v>29</v>
       </c>
       <c r="W18" s="2"/>
-    </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X18" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -3339,8 +3392,11 @@
         <v>29</v>
       </c>
       <c r="W19" s="2"/>
-    </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X19" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -3408,8 +3464,11 @@
         <v>29</v>
       </c>
       <c r="W20" s="2"/>
-    </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X20" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -3477,8 +3536,11 @@
         <v>29</v>
       </c>
       <c r="W21" s="2"/>
-    </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X21" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -3546,8 +3608,11 @@
         <v>29</v>
       </c>
       <c r="W22" s="2"/>
-    </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X22" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -3615,8 +3680,11 @@
         <v>29</v>
       </c>
       <c r="W23" s="2"/>
-    </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X23" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -3684,8 +3752,11 @@
         <v>29</v>
       </c>
       <c r="W24" s="2"/>
-    </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X24" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -3753,8 +3824,11 @@
         <v>29</v>
       </c>
       <c r="W25" s="2"/>
-    </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X25" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -3822,8 +3896,11 @@
         <v>29</v>
       </c>
       <c r="W26" s="2"/>
-    </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X26" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="27" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
@@ -3891,8 +3968,11 @@
         <v>29</v>
       </c>
       <c r="W27" s="2"/>
-    </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X27" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="28" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -3960,8 +4040,11 @@
         <v>29</v>
       </c>
       <c r="W28" s="2"/>
-    </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X28" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -4029,8 +4112,11 @@
         <v>29</v>
       </c>
       <c r="W29" s="2"/>
-    </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X29" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
@@ -4098,8 +4184,11 @@
         <v>29</v>
       </c>
       <c r="W30" s="2"/>
-    </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X30" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
@@ -4167,8 +4256,11 @@
         <v>147</v>
       </c>
       <c r="W31" s="2"/>
-    </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X31" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="32" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
@@ -4236,8 +4328,11 @@
         <v>147</v>
       </c>
       <c r="W32" s="2"/>
-    </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X32" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
@@ -4305,8 +4400,11 @@
         <v>147</v>
       </c>
       <c r="W33" s="2"/>
-    </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X33" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="34" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
@@ -4374,8 +4472,11 @@
         <v>147</v>
       </c>
       <c r="W34" s="2"/>
-    </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X34" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="35" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
@@ -4443,8 +4544,11 @@
         <v>147</v>
       </c>
       <c r="W35" s="2"/>
-    </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X35" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="36" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
@@ -4512,8 +4616,11 @@
         <v>147</v>
       </c>
       <c r="W36" s="2"/>
-    </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X36" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="37" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
@@ -4581,8 +4688,11 @@
         <v>29</v>
       </c>
       <c r="W37" s="2"/>
-    </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X37" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="38" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
@@ -4646,8 +4756,11 @@
       <c r="U38" s="2"/>
       <c r="V38" s="2"/>
       <c r="W38" s="2"/>
-    </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X38" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="39" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
       </c>
@@ -4715,8 +4828,11 @@
         <v>29</v>
       </c>
       <c r="W39" s="2"/>
-    </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X39" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="40" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>39</v>
       </c>
@@ -4784,8 +4900,11 @@
         <v>29</v>
       </c>
       <c r="W40" s="2"/>
-    </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X40" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="41" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>40</v>
       </c>
@@ -4853,8 +4972,11 @@
         <v>29</v>
       </c>
       <c r="W41" s="2"/>
-    </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X41" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="42" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>41</v>
       </c>
@@ -4922,8 +5044,11 @@
         <v>29</v>
       </c>
       <c r="W42" s="2"/>
-    </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X42" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="43" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>42</v>
       </c>
@@ -4991,8 +5116,11 @@
         <v>29</v>
       </c>
       <c r="W43" s="2"/>
-    </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X43" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="44" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>43</v>
       </c>
@@ -5060,8 +5188,11 @@
         <v>29</v>
       </c>
       <c r="W44" s="2"/>
-    </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X44" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="45" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>44</v>
       </c>
@@ -5129,8 +5260,11 @@
         <v>29</v>
       </c>
       <c r="W45" s="2"/>
-    </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X45" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="46" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>45</v>
       </c>
@@ -5198,8 +5332,11 @@
         <v>29</v>
       </c>
       <c r="W46" s="2"/>
-    </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X46" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="47" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>46</v>
       </c>
@@ -5267,8 +5404,11 @@
         <v>29</v>
       </c>
       <c r="W47" s="2"/>
-    </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X47" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="48" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>47</v>
       </c>
@@ -5336,8 +5476,11 @@
         <v>29</v>
       </c>
       <c r="W48" s="2"/>
-    </row>
-    <row r="49" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X48" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="49" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>48</v>
       </c>
@@ -5405,8 +5548,11 @@
         <v>29</v>
       </c>
       <c r="W49" s="2"/>
-    </row>
-    <row r="50" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X49" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="50" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>49</v>
       </c>
@@ -5474,8 +5620,11 @@
         <v>29</v>
       </c>
       <c r="W50" s="2"/>
-    </row>
-    <row r="51" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X50" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="51" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>50</v>
       </c>
@@ -5543,8 +5692,11 @@
         <v>29</v>
       </c>
       <c r="W51" s="2"/>
-    </row>
-    <row r="52" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X51" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="52" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>51</v>
       </c>
@@ -5612,8 +5764,11 @@
         <v>29</v>
       </c>
       <c r="W52" s="2"/>
-    </row>
-    <row r="53" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X52" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="53" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>52</v>
       </c>
@@ -5681,8 +5836,11 @@
         <v>29</v>
       </c>
       <c r="W53" s="2"/>
-    </row>
-    <row r="54" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X53" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="54" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>53</v>
       </c>
@@ -5750,8 +5908,11 @@
         <v>29</v>
       </c>
       <c r="W54" s="2"/>
-    </row>
-    <row r="55" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X54" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="55" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>54</v>
       </c>
@@ -5819,8 +5980,11 @@
         <v>29</v>
       </c>
       <c r="W55" s="2"/>
-    </row>
-    <row r="56" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X55" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="56" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>55</v>
       </c>
@@ -5888,8 +6052,11 @@
         <v>29</v>
       </c>
       <c r="W56" s="2"/>
-    </row>
-    <row r="57" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X56" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="57" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>56</v>
       </c>
@@ -5957,8 +6124,11 @@
         <v>29</v>
       </c>
       <c r="W57" s="2"/>
-    </row>
-    <row r="58" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X57" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="58" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>57</v>
       </c>
@@ -6026,8 +6196,11 @@
         <v>29</v>
       </c>
       <c r="W58" s="2"/>
-    </row>
-    <row r="59" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X58" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="59" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>58</v>
       </c>
@@ -6095,8 +6268,11 @@
         <v>29</v>
       </c>
       <c r="W59" s="2"/>
-    </row>
-    <row r="60" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X59" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="60" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>59</v>
       </c>
@@ -6164,8 +6340,11 @@
         <v>29</v>
       </c>
       <c r="W60" s="2"/>
-    </row>
-    <row r="61" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X60" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="61" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>60</v>
       </c>
@@ -6233,8 +6412,11 @@
         <v>29</v>
       </c>
       <c r="W61" s="2"/>
-    </row>
-    <row r="62" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X61" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="62" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>61</v>
       </c>
@@ -6302,8 +6484,11 @@
         <v>29</v>
       </c>
       <c r="W62" s="2"/>
-    </row>
-    <row r="63" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X62" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="63" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>62</v>
       </c>
@@ -6371,8 +6556,11 @@
         <v>29</v>
       </c>
       <c r="W63" s="2"/>
-    </row>
-    <row r="64" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X63" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="64" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>63</v>
       </c>
@@ -6440,8 +6628,11 @@
         <v>29</v>
       </c>
       <c r="W64" s="2"/>
-    </row>
-    <row r="65" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X64" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="65" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>64</v>
       </c>
@@ -6509,8 +6700,11 @@
         <v>29</v>
       </c>
       <c r="W65" s="2"/>
-    </row>
-    <row r="66" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X65" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="66" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>65</v>
       </c>
@@ -6578,8 +6772,11 @@
         <v>29</v>
       </c>
       <c r="W66" s="2"/>
-    </row>
-    <row r="67" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X66" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="67" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>66</v>
       </c>
@@ -6645,8 +6842,11 @@
         <v>29</v>
       </c>
       <c r="W67" s="2"/>
-    </row>
-    <row r="68" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X67" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="68" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>67</v>
       </c>
@@ -6712,8 +6912,11 @@
         <v>29</v>
       </c>
       <c r="W68" s="2"/>
-    </row>
-    <row r="69" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X68" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="69" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>68</v>
       </c>
@@ -6781,8 +6984,11 @@
         <v>29</v>
       </c>
       <c r="W69" s="2"/>
-    </row>
-    <row r="70" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X69" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="70" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>69</v>
       </c>
@@ -6850,8 +7056,11 @@
         <v>29</v>
       </c>
       <c r="W70" s="2"/>
-    </row>
-    <row r="71" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X70" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="71" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>70</v>
       </c>
@@ -6919,8 +7128,11 @@
         <v>29</v>
       </c>
       <c r="W71" s="2"/>
-    </row>
-    <row r="72" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X71" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="72" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>71</v>
       </c>
@@ -6988,8 +7200,11 @@
         <v>29</v>
       </c>
       <c r="W72" s="2"/>
-    </row>
-    <row r="73" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X72" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="73" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>72</v>
       </c>
@@ -7057,8 +7272,11 @@
         <v>29</v>
       </c>
       <c r="W73" s="2"/>
-    </row>
-    <row r="74" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X73" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="74" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>73</v>
       </c>
@@ -7126,8 +7344,11 @@
         <v>29</v>
       </c>
       <c r="W74" s="2"/>
-    </row>
-    <row r="75" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X74" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="75" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>74</v>
       </c>
@@ -7195,8 +7416,11 @@
         <v>29</v>
       </c>
       <c r="W75" s="2"/>
-    </row>
-    <row r="76" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X75" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="76" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>75</v>
       </c>
@@ -7264,8 +7488,11 @@
         <v>29</v>
       </c>
       <c r="W76" s="2"/>
-    </row>
-    <row r="77" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X76" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="77" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>76</v>
       </c>
@@ -7333,8 +7560,11 @@
         <v>29</v>
       </c>
       <c r="W77" s="2"/>
-    </row>
-    <row r="78" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X77" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="78" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>77</v>
       </c>
@@ -7402,8 +7632,11 @@
         <v>29</v>
       </c>
       <c r="W78" s="2"/>
-    </row>
-    <row r="79" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X78" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="79" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>78</v>
       </c>
@@ -7471,8 +7704,11 @@
         <v>29</v>
       </c>
       <c r="W79" s="2"/>
-    </row>
-    <row r="80" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X79" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="80" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>79</v>
       </c>
@@ -7540,8 +7776,11 @@
         <v>29</v>
       </c>
       <c r="W80" s="2"/>
-    </row>
-    <row r="81" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X80" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="81" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>80</v>
       </c>
@@ -7607,8 +7846,11 @@
         <v>29</v>
       </c>
       <c r="W81" s="2"/>
-    </row>
-    <row r="82" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X81" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="82" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>82</v>
       </c>
@@ -7676,8 +7918,11 @@
         <v>29</v>
       </c>
       <c r="W82" s="2"/>
-    </row>
-    <row r="83" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X82" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="83" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>83</v>
       </c>
@@ -7745,8 +7990,11 @@
         <v>29</v>
       </c>
       <c r="W83" s="2"/>
-    </row>
-    <row r="84" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X83" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="84" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>84</v>
       </c>
@@ -7814,8 +8062,11 @@
         <v>29</v>
       </c>
       <c r="W84" s="2"/>
-    </row>
-    <row r="85" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X84" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="85" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>85</v>
       </c>
@@ -7883,8 +8134,11 @@
         <v>29</v>
       </c>
       <c r="W85" s="2"/>
-    </row>
-    <row r="86" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X85" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="86" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>86</v>
       </c>
@@ -7952,8 +8206,11 @@
         <v>29</v>
       </c>
       <c r="W86" s="2"/>
-    </row>
-    <row r="87" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X86" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="87" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>87</v>
       </c>
@@ -8021,8 +8278,11 @@
         <v>29</v>
       </c>
       <c r="W87" s="2"/>
-    </row>
-    <row r="88" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X87" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="88" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>88</v>
       </c>
@@ -8088,8 +8348,11 @@
         <v>29</v>
       </c>
       <c r="W88" s="2"/>
-    </row>
-    <row r="89" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X88" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="89" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>89</v>
       </c>
@@ -8155,8 +8418,11 @@
         <v>29</v>
       </c>
       <c r="W89" s="2"/>
-    </row>
-    <row r="90" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X89" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="90" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>90</v>
       </c>
@@ -8224,8 +8490,11 @@
         <v>29</v>
       </c>
       <c r="W90" s="2"/>
-    </row>
-    <row r="91" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X90" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="91" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>91</v>
       </c>
@@ -8293,8 +8562,11 @@
         <v>29</v>
       </c>
       <c r="W91" s="2"/>
-    </row>
-    <row r="92" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X91" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="92" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>92</v>
       </c>
@@ -8362,8 +8634,11 @@
         <v>29</v>
       </c>
       <c r="W92" s="2"/>
-    </row>
-    <row r="93" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X92" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="93" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>93</v>
       </c>
@@ -8431,8 +8706,11 @@
         <v>29</v>
       </c>
       <c r="W93" s="2"/>
-    </row>
-    <row r="94" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X93" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="94" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>94</v>
       </c>
@@ -8500,8 +8778,11 @@
         <v>29</v>
       </c>
       <c r="W94" s="2"/>
-    </row>
-    <row r="95" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X94" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="95" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>95</v>
       </c>
@@ -8569,8 +8850,11 @@
         <v>29</v>
       </c>
       <c r="W95" s="2"/>
-    </row>
-    <row r="96" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X95" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="96" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>96</v>
       </c>
@@ -8638,8 +8922,11 @@
         <v>29</v>
       </c>
       <c r="W96" s="2"/>
-    </row>
-    <row r="97" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X96" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="97" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>97</v>
       </c>
@@ -8707,8 +8994,11 @@
         <v>29</v>
       </c>
       <c r="W97" s="2"/>
-    </row>
-    <row r="98" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X97" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="98" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>98</v>
       </c>
@@ -8776,8 +9066,11 @@
         <v>29</v>
       </c>
       <c r="W98" s="2"/>
-    </row>
-    <row r="99" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X98" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="99" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>99</v>
       </c>
@@ -8845,8 +9138,11 @@
         <v>29</v>
       </c>
       <c r="W99" s="2"/>
-    </row>
-    <row r="100" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X99" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="100" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>100</v>
       </c>
@@ -8914,8 +9210,11 @@
         <v>29</v>
       </c>
       <c r="W100" s="14"/>
-    </row>
-    <row r="101" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X100" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="101" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>101</v>
       </c>
@@ -8983,8 +9282,11 @@
         <v>29</v>
       </c>
       <c r="W101" s="14"/>
-    </row>
-    <row r="102" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X101" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="102" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>102</v>
       </c>
@@ -9052,8 +9354,11 @@
         <v>29</v>
       </c>
       <c r="W102" s="14"/>
-    </row>
-    <row r="103" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X102" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="103" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>103</v>
       </c>
@@ -9121,8 +9426,11 @@
         <v>29</v>
       </c>
       <c r="W103" s="14"/>
-    </row>
-    <row r="104" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X103" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="104" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>104</v>
       </c>
@@ -9190,8 +9498,11 @@
         <v>29</v>
       </c>
       <c r="W104" s="14"/>
-    </row>
-    <row r="105" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X104" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="105" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>105</v>
       </c>
@@ -9259,8 +9570,11 @@
         <v>29</v>
       </c>
       <c r="W105" s="14"/>
-    </row>
-    <row r="106" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X105" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="106" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>106</v>
       </c>
@@ -9328,8 +9642,11 @@
         <v>29</v>
       </c>
       <c r="W106" s="14"/>
-    </row>
-    <row r="107" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X106" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="107" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>107</v>
       </c>
@@ -9397,8 +9714,11 @@
         <v>29</v>
       </c>
       <c r="W107" s="14"/>
-    </row>
-    <row r="108" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X107" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="108" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>108</v>
       </c>
@@ -9466,8 +9786,11 @@
         <v>29</v>
       </c>
       <c r="W108" s="14"/>
-    </row>
-    <row r="109" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X108" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="109" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>109</v>
       </c>
@@ -9535,8 +9858,11 @@
         <v>29</v>
       </c>
       <c r="W109" s="14"/>
-    </row>
-    <row r="110" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X109" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="110" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>110</v>
       </c>
@@ -9604,8 +9930,11 @@
         <v>29</v>
       </c>
       <c r="W110" s="14"/>
-    </row>
-    <row r="111" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X110" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="111" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>111</v>
       </c>
@@ -9671,8 +10000,11 @@
         <v>29</v>
       </c>
       <c r="W111" s="14"/>
-    </row>
-    <row r="112" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X111" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="112" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>112</v>
       </c>
@@ -9740,8 +10072,11 @@
         <v>29</v>
       </c>
       <c r="W112" s="14"/>
-    </row>
-    <row r="113" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X112" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="113" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>113</v>
       </c>
@@ -9809,8 +10144,11 @@
         <v>29</v>
       </c>
       <c r="W113" s="2"/>
-    </row>
-    <row r="114" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X113" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="114" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>114</v>
       </c>
@@ -9878,8 +10216,11 @@
         <v>29</v>
       </c>
       <c r="W114" s="2"/>
-    </row>
-    <row r="115" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X114" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="115" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>115</v>
       </c>
@@ -9947,8 +10288,11 @@
         <v>29</v>
       </c>
       <c r="W115" s="2"/>
-    </row>
-    <row r="116" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X115" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="116" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>116</v>
       </c>
@@ -10016,8 +10360,11 @@
         <v>29</v>
       </c>
       <c r="W116" s="2"/>
-    </row>
-    <row r="117" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X116" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="117" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>117</v>
       </c>
@@ -10085,8 +10432,11 @@
         <v>29</v>
       </c>
       <c r="W117" s="2"/>
-    </row>
-    <row r="118" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X117" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="118" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>118</v>
       </c>
@@ -10154,8 +10504,11 @@
         <v>29</v>
       </c>
       <c r="W118" s="2"/>
-    </row>
-    <row r="119" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X118" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="119" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>119</v>
       </c>
@@ -10221,8 +10574,11 @@
         <v>29</v>
       </c>
       <c r="W119" s="2"/>
-    </row>
-    <row r="120" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X119" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="120" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>120</v>
       </c>
@@ -10290,8 +10646,11 @@
         <v>29</v>
       </c>
       <c r="W120" s="2"/>
-    </row>
-    <row r="121" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X120" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="121" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>121</v>
       </c>
@@ -10359,8 +10718,11 @@
         <v>29</v>
       </c>
       <c r="W121" s="2"/>
-    </row>
-    <row r="122" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X121" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="122" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>122</v>
       </c>
@@ -10428,8 +10790,11 @@
         <v>29</v>
       </c>
       <c r="W122" s="2"/>
-    </row>
-    <row r="123" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X122" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="123" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>123</v>
       </c>
@@ -10497,8 +10862,11 @@
         <v>29</v>
       </c>
       <c r="W123" s="2"/>
-    </row>
-    <row r="124" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X123" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="124" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>124</v>
       </c>
@@ -10566,8 +10934,11 @@
         <v>29</v>
       </c>
       <c r="W124" s="2"/>
-    </row>
-    <row r="125" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X124" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="125" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>125</v>
       </c>
@@ -10635,8 +11006,11 @@
         <v>29</v>
       </c>
       <c r="W125" s="2"/>
-    </row>
-    <row r="126" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X125" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="126" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>126</v>
       </c>
@@ -10704,8 +11078,11 @@
         <v>29</v>
       </c>
       <c r="W126" s="2"/>
-    </row>
-    <row r="127" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X126" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="127" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>127</v>
       </c>
@@ -10773,8 +11150,11 @@
         <v>29</v>
       </c>
       <c r="W127" s="2"/>
-    </row>
-    <row r="128" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X127" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="128" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>128</v>
       </c>
@@ -10842,8 +11222,11 @@
         <v>29</v>
       </c>
       <c r="W128" s="2"/>
-    </row>
-    <row r="129" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X128" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="129" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>129</v>
       </c>
@@ -10911,8 +11294,11 @@
         <v>29</v>
       </c>
       <c r="W129" s="2"/>
-    </row>
-    <row r="130" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X129" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="130" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>130</v>
       </c>
@@ -10980,8 +11366,11 @@
         <v>29</v>
       </c>
       <c r="W130" s="2"/>
-    </row>
-    <row r="131" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X130" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="131" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>131</v>
       </c>
@@ -11049,8 +11438,11 @@
         <v>29</v>
       </c>
       <c r="W131" s="2"/>
-    </row>
-    <row r="132" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X131" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="132" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>132</v>
       </c>
@@ -11118,8 +11510,11 @@
         <v>29</v>
       </c>
       <c r="W132" s="2"/>
-    </row>
-    <row r="133" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X132" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="133" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>133</v>
       </c>
@@ -11185,8 +11580,11 @@
         <v>29</v>
       </c>
       <c r="W133" s="2"/>
-    </row>
-    <row r="134" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X133" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="134" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>134</v>
       </c>
@@ -11252,8 +11650,11 @@
         <v>29</v>
       </c>
       <c r="W134" s="2"/>
-    </row>
-    <row r="135" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X134" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="135" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>135</v>
       </c>
@@ -11319,8 +11720,11 @@
         <v>29</v>
       </c>
       <c r="W135" s="2"/>
-    </row>
-    <row r="136" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X135" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="136" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>136</v>
       </c>
@@ -11386,8 +11790,11 @@
         <v>29</v>
       </c>
       <c r="W136" s="2"/>
-    </row>
-    <row r="137" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X136" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="137" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>137</v>
       </c>
@@ -11455,8 +11862,11 @@
         <v>29</v>
       </c>
       <c r="W137" s="2"/>
-    </row>
-    <row r="138" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X137" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="138" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>138</v>
       </c>
@@ -11524,8 +11934,11 @@
         <v>29</v>
       </c>
       <c r="W138" s="2"/>
-    </row>
-    <row r="139" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X138" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="139" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>139</v>
       </c>
@@ -11593,8 +12006,11 @@
         <v>29</v>
       </c>
       <c r="W139" s="2"/>
-    </row>
-    <row r="140" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X139" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="140" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>140</v>
       </c>
@@ -11662,8 +12078,11 @@
         <v>29</v>
       </c>
       <c r="W140" s="2"/>
-    </row>
-    <row r="141" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X140" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="141" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>141</v>
       </c>
@@ -11731,8 +12150,11 @@
         <v>29</v>
       </c>
       <c r="W141" s="2"/>
-    </row>
-    <row r="142" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X141" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="142" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>142</v>
       </c>
@@ -11800,8 +12222,11 @@
         <v>29</v>
       </c>
       <c r="W142" s="2"/>
-    </row>
-    <row r="143" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X142" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="143" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>143</v>
       </c>
@@ -11869,8 +12294,11 @@
         <v>29</v>
       </c>
       <c r="W143" s="2"/>
-    </row>
-    <row r="144" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X143" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="144" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>144</v>
       </c>
@@ -11938,8 +12366,11 @@
         <v>29</v>
       </c>
       <c r="W144" s="2"/>
-    </row>
-    <row r="145" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X144" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="145" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>145</v>
       </c>
@@ -12005,8 +12436,11 @@
         <v>29</v>
       </c>
       <c r="W145" s="2"/>
-    </row>
-    <row r="146" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X145" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="146" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>146</v>
       </c>
@@ -12074,8 +12508,11 @@
         <v>29</v>
       </c>
       <c r="W146" s="2"/>
-    </row>
-    <row r="147" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X146" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="147" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>147</v>
       </c>
@@ -12143,8 +12580,11 @@
         <v>29</v>
       </c>
       <c r="W147" s="2"/>
-    </row>
-    <row r="148" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X147" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="148" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>148</v>
       </c>
@@ -12212,8 +12652,11 @@
         <v>29</v>
       </c>
       <c r="W148" s="2"/>
-    </row>
-    <row r="149" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X148" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="149" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>149</v>
       </c>
@@ -12281,8 +12724,11 @@
         <v>29</v>
       </c>
       <c r="W149" s="2"/>
-    </row>
-    <row r="150" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X149" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="150" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>150</v>
       </c>
@@ -12350,8 +12796,11 @@
         <v>29</v>
       </c>
       <c r="W150" s="2"/>
-    </row>
-    <row r="151" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X150" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="151" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>151</v>
       </c>
@@ -12419,8 +12868,11 @@
         <v>29</v>
       </c>
       <c r="W151" s="2"/>
-    </row>
-    <row r="152" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X151" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="152" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>152</v>
       </c>
@@ -12488,8 +12940,11 @@
         <v>29</v>
       </c>
       <c r="W152" s="2"/>
-    </row>
-    <row r="153" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X152" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="153" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>153</v>
       </c>
@@ -12557,8 +13012,11 @@
         <v>29</v>
       </c>
       <c r="W153" s="2"/>
-    </row>
-    <row r="154" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X153" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="154" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>154</v>
       </c>
@@ -12626,8 +13084,11 @@
         <v>29</v>
       </c>
       <c r="W154" s="2"/>
-    </row>
-    <row r="155" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X154" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="155" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>155</v>
       </c>
@@ -12695,8 +13156,11 @@
         <v>29</v>
       </c>
       <c r="W155" s="2"/>
-    </row>
-    <row r="156" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X155" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="156" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>156</v>
       </c>
@@ -12764,8 +13228,11 @@
         <v>29</v>
       </c>
       <c r="W156" s="2"/>
-    </row>
-    <row r="157" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X156" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="157" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>157</v>
       </c>
@@ -12833,8 +13300,11 @@
         <v>29</v>
       </c>
       <c r="W157" s="2"/>
-    </row>
-    <row r="158" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X157" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="158" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>158</v>
       </c>
@@ -12902,8 +13372,11 @@
         <v>29</v>
       </c>
       <c r="W158" s="2"/>
-    </row>
-    <row r="159" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X158" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="159" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>159</v>
       </c>
@@ -12971,8 +13444,11 @@
         <v>29</v>
       </c>
       <c r="W159" s="2"/>
-    </row>
-    <row r="160" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X159" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="160" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>160</v>
       </c>
@@ -13040,8 +13516,11 @@
         <v>29</v>
       </c>
       <c r="W160" s="2"/>
-    </row>
-    <row r="161" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X160" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="161" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>161</v>
       </c>
@@ -13109,8 +13588,11 @@
         <v>29</v>
       </c>
       <c r="W161" s="2"/>
-    </row>
-    <row r="162" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X161" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="162" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>162</v>
       </c>
@@ -13178,8 +13660,11 @@
         <v>29</v>
       </c>
       <c r="W162" s="2"/>
-    </row>
-    <row r="163" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X162" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="163" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>163</v>
       </c>
@@ -13247,8 +13732,11 @@
         <v>29</v>
       </c>
       <c r="W163" s="2"/>
-    </row>
-    <row r="164" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X163" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="164" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>164</v>
       </c>
@@ -13316,8 +13804,11 @@
         <v>29</v>
       </c>
       <c r="W164" s="2"/>
-    </row>
-    <row r="165" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X164" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="165" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>165</v>
       </c>
@@ -13385,8 +13876,11 @@
         <v>29</v>
       </c>
       <c r="W165" s="2"/>
-    </row>
-    <row r="166" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X165" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="166" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>166</v>
       </c>
@@ -13454,8 +13948,11 @@
         <v>29</v>
       </c>
       <c r="W166" s="2"/>
-    </row>
-    <row r="167" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X166" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="167" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>167</v>
       </c>
@@ -13522,8 +14019,11 @@
       <c r="V167" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="168" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X167" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="168" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>168</v>
       </c>
@@ -13590,8 +14090,11 @@
       <c r="V168" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="169" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X168" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="169" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>169</v>
       </c>
@@ -13658,8 +14161,11 @@
       <c r="V169" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="170" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X169" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="170" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>170</v>
       </c>
@@ -13726,8 +14232,11 @@
       <c r="V170" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="171" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X170" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="171" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>171</v>
       </c>
@@ -13794,8 +14303,11 @@
       <c r="V171" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="172" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X171" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="172" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>172</v>
       </c>
@@ -13862,8 +14374,11 @@
       <c r="V172" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="173" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X172" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="173" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>173</v>
       </c>
@@ -13930,8 +14445,11 @@
       <c r="V173" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="174" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X173" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="174" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>174</v>
       </c>
@@ -13998,8 +14516,11 @@
       <c r="V174" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="175" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X174" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="175" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>175</v>
       </c>
@@ -14066,8 +14587,11 @@
       <c r="V175" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="176" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X175" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="176" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>176</v>
       </c>
@@ -14134,8 +14658,11 @@
       <c r="V176" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="177" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X176" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="177" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>177</v>
       </c>
@@ -14202,8 +14729,11 @@
       <c r="V177" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="178" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X177" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="178" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>178</v>
       </c>
@@ -14270,8 +14800,11 @@
       <c r="V178" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="179" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X178" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="179" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>179</v>
       </c>
@@ -14338,8 +14871,11 @@
       <c r="V179" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="180" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X179" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="180" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>180</v>
       </c>
@@ -14406,8 +14942,11 @@
       <c r="V180" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="181" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X180" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="181" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>181</v>
       </c>
@@ -14474,8 +15013,11 @@
       <c r="V181" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="182" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X181" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="182" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>182</v>
       </c>
@@ -14542,8 +15084,11 @@
       <c r="V182" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="183" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X182" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="183" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>183</v>
       </c>
@@ -14611,8 +15156,11 @@
         <v>29</v>
       </c>
       <c r="W183" s="2"/>
-    </row>
-    <row r="184" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X183" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="184" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>184</v>
       </c>
@@ -14680,8 +15228,11 @@
         <v>29</v>
       </c>
       <c r="W184" s="2"/>
-    </row>
-    <row r="185" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X184" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="185" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>185</v>
       </c>
@@ -14749,8 +15300,11 @@
         <v>29</v>
       </c>
       <c r="W185" s="2"/>
-    </row>
-    <row r="186" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X185" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="186" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>186</v>
       </c>
@@ -14818,8 +15372,11 @@
         <v>29</v>
       </c>
       <c r="W186" s="2"/>
-    </row>
-    <row r="187" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X186" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="187" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>187</v>
       </c>
@@ -14887,8 +15444,11 @@
         <v>29</v>
       </c>
       <c r="W187" s="2"/>
-    </row>
-    <row r="188" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X187" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="188" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>188</v>
       </c>
@@ -14956,8 +15516,11 @@
         <v>29</v>
       </c>
       <c r="W188" s="2"/>
-    </row>
-    <row r="189" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X188" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="189" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A189">
         <v>189</v>
       </c>
@@ -15025,8 +15588,11 @@
         <v>29</v>
       </c>
       <c r="W189" s="2"/>
-    </row>
-    <row r="190" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X189" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="190" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>190</v>
       </c>
@@ -15094,8 +15660,11 @@
         <v>29</v>
       </c>
       <c r="W190" s="2"/>
-    </row>
-    <row r="191" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X190" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="191" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>191</v>
       </c>
@@ -15163,8 +15732,11 @@
         <v>29</v>
       </c>
       <c r="W191" s="2"/>
-    </row>
-    <row r="192" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X191" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="192" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>192</v>
       </c>
@@ -15232,8 +15804,11 @@
         <v>29</v>
       </c>
       <c r="W192" s="2"/>
-    </row>
-    <row r="193" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X192" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="193" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>193</v>
       </c>
@@ -15301,8 +15876,11 @@
         <v>29</v>
       </c>
       <c r="W193" s="2"/>
-    </row>
-    <row r="194" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X193" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="194" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>194</v>
       </c>
@@ -15370,8 +15948,11 @@
         <v>29</v>
       </c>
       <c r="W194" s="2"/>
-    </row>
-    <row r="195" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X194" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="195" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>195</v>
       </c>
@@ -15439,8 +16020,11 @@
         <v>29</v>
       </c>
       <c r="W195" s="2"/>
-    </row>
-    <row r="196" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X195" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="196" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A196">
         <v>196</v>
       </c>
@@ -15508,8 +16092,11 @@
         <v>29</v>
       </c>
       <c r="W196" s="2"/>
-    </row>
-    <row r="197" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X196" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="197" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A197">
         <v>197</v>
       </c>
@@ -15577,8 +16164,11 @@
         <v>29</v>
       </c>
       <c r="W197" s="2"/>
-    </row>
-    <row r="198" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X197" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="198" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A198">
         <v>198</v>
       </c>
@@ -15646,8 +16236,11 @@
         <v>29</v>
       </c>
       <c r="W198" s="2"/>
-    </row>
-    <row r="199" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X198" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="199" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>199</v>
       </c>
@@ -15715,8 +16308,11 @@
         <v>29</v>
       </c>
       <c r="W199" s="2"/>
-    </row>
-    <row r="200" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X199" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="200" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A200">
         <v>200</v>
       </c>
@@ -15784,8 +16380,11 @@
         <v>29</v>
       </c>
       <c r="W200" s="2"/>
-    </row>
-    <row r="201" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X200" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="201" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A201">
         <v>201</v>
       </c>
@@ -15853,8 +16452,11 @@
         <v>29</v>
       </c>
       <c r="W201" s="2"/>
-    </row>
-    <row r="202" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X201" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="202" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A202">
         <v>202</v>
       </c>
@@ -15922,8 +16524,11 @@
         <v>29</v>
       </c>
       <c r="W202" s="2"/>
-    </row>
-    <row r="203" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X202" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="203" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A203">
         <v>203</v>
       </c>
@@ -15991,8 +16596,11 @@
         <v>29</v>
       </c>
       <c r="W203" s="2"/>
-    </row>
-    <row r="204" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X203" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="204" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A204">
         <v>204</v>
       </c>
@@ -16060,8 +16668,11 @@
         <v>29</v>
       </c>
       <c r="W204" s="2"/>
-    </row>
-    <row r="205" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X204" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="205" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>205</v>
       </c>
@@ -16129,8 +16740,11 @@
         <v>29</v>
       </c>
       <c r="W205" s="2"/>
-    </row>
-    <row r="206" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X205" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="206" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>206</v>
       </c>
@@ -16198,8 +16812,11 @@
         <v>29</v>
       </c>
       <c r="W206" s="2"/>
-    </row>
-    <row r="207" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X206" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="207" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>207</v>
       </c>
@@ -16267,8 +16884,11 @@
         <v>29</v>
       </c>
       <c r="W207" s="2"/>
-    </row>
-    <row r="208" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X207" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="208" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>208</v>
       </c>
@@ -16336,8 +16956,11 @@
         <v>29</v>
       </c>
       <c r="W208" s="2"/>
-    </row>
-    <row r="209" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X208" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="209" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>209</v>
       </c>
@@ -16405,8 +17028,11 @@
         <v>29</v>
       </c>
       <c r="W209" s="2"/>
-    </row>
-    <row r="210" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X209" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="210" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>210</v>
       </c>
@@ -16474,8 +17100,11 @@
         <v>29</v>
       </c>
       <c r="W210" s="2"/>
-    </row>
-    <row r="211" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X210" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="211" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>211</v>
       </c>
@@ -16543,8 +17172,11 @@
         <v>29</v>
       </c>
       <c r="W211" s="2"/>
-    </row>
-    <row r="212" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X211" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="212" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>212</v>
       </c>
@@ -16612,8 +17244,11 @@
         <v>29</v>
       </c>
       <c r="W212" s="2"/>
-    </row>
-    <row r="213" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X212" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="213" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A213">
         <v>213</v>
       </c>
@@ -16681,8 +17316,11 @@
         <v>29</v>
       </c>
       <c r="W213" s="2"/>
-    </row>
-    <row r="214" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X213" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="214" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A214">
         <v>214</v>
       </c>
@@ -16750,8 +17388,11 @@
         <v>29</v>
       </c>
       <c r="W214" s="2"/>
-    </row>
-    <row r="215" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X214" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="215" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A215">
         <v>215</v>
       </c>
@@ -16819,8 +17460,11 @@
         <v>29</v>
       </c>
       <c r="W215" s="2"/>
-    </row>
-    <row r="216" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X215" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="216" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>216</v>
       </c>
@@ -16888,8 +17532,11 @@
         <v>29</v>
       </c>
       <c r="W216" s="2"/>
-    </row>
-    <row r="217" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X216" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="217" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>217</v>
       </c>
@@ -16957,8 +17604,11 @@
         <v>29</v>
       </c>
       <c r="W217" s="2"/>
-    </row>
-    <row r="218" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X217" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="218" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>218</v>
       </c>
@@ -17026,8 +17676,11 @@
         <v>29</v>
       </c>
       <c r="W218" s="2"/>
-    </row>
-    <row r="219" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X218" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="219" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>219</v>
       </c>
@@ -17095,8 +17748,11 @@
         <v>29</v>
       </c>
       <c r="W219" s="2"/>
-    </row>
-    <row r="220" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X219" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="220" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>220</v>
       </c>
@@ -17164,8 +17820,11 @@
         <v>29</v>
       </c>
       <c r="W220" s="2"/>
-    </row>
-    <row r="221" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X220" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="221" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A221">
         <v>221</v>
       </c>
@@ -17233,8 +17892,11 @@
         <v>29</v>
       </c>
       <c r="W221" s="2"/>
-    </row>
-    <row r="222" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X221" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="222" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A222">
         <v>222</v>
       </c>
@@ -17302,8 +17964,11 @@
         <v>29</v>
       </c>
       <c r="W222" s="2"/>
-    </row>
-    <row r="223" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X222" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="223" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A223">
         <v>223</v>
       </c>
@@ -17371,8 +18036,11 @@
         <v>29</v>
       </c>
       <c r="W223" s="2"/>
-    </row>
-    <row r="224" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X223" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="224" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A224">
         <v>224</v>
       </c>
@@ -17440,8 +18108,11 @@
         <v>29</v>
       </c>
       <c r="W224" s="2"/>
-    </row>
-    <row r="225" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X224" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="225" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>225</v>
       </c>
@@ -17509,8 +18180,11 @@
         <v>29</v>
       </c>
       <c r="W225" s="2"/>
-    </row>
-    <row r="226" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X225" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="226" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>226</v>
       </c>
@@ -17575,8 +18249,11 @@
         <v>29</v>
       </c>
       <c r="W226" s="2"/>
-    </row>
-    <row r="227" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X226" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="227" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A227">
         <v>227</v>
       </c>
@@ -17644,8 +18321,11 @@
         <v>29</v>
       </c>
       <c r="W227" s="2"/>
-    </row>
-    <row r="228" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X227" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="228" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A228">
         <v>228</v>
       </c>
@@ -17713,8 +18393,11 @@
         <v>29</v>
       </c>
       <c r="W228" s="2"/>
-    </row>
-    <row r="229" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X228" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="229" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A229">
         <v>229</v>
       </c>
@@ -17782,8 +18465,11 @@
         <v>29</v>
       </c>
       <c r="W229" s="2"/>
-    </row>
-    <row r="230" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X229" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="230" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A230">
         <v>230</v>
       </c>
@@ -17851,8 +18537,11 @@
         <v>29</v>
       </c>
       <c r="W230" s="2"/>
-    </row>
-    <row r="231" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X230" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="231" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A231">
         <v>231</v>
       </c>
@@ -17920,8 +18609,11 @@
         <v>29</v>
       </c>
       <c r="W231" s="2"/>
-    </row>
-    <row r="232" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X231" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="232" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A232">
         <v>232</v>
       </c>
@@ -17989,8 +18681,11 @@
         <v>29</v>
       </c>
       <c r="W232" s="2"/>
-    </row>
-    <row r="233" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X232" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="233" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A233">
         <v>233</v>
       </c>
@@ -18058,8 +18753,11 @@
         <v>29</v>
       </c>
       <c r="W233" s="2"/>
-    </row>
-    <row r="234" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X233" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="234" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A234">
         <v>234</v>
       </c>
@@ -18127,8 +18825,11 @@
         <v>29</v>
       </c>
       <c r="W234" s="2"/>
-    </row>
-    <row r="235" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X234" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="235" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A235">
         <v>235</v>
       </c>
@@ -18196,8 +18897,11 @@
         <v>29</v>
       </c>
       <c r="W235" s="2"/>
-    </row>
-    <row r="236" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X235" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="236" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A236">
         <v>236</v>
       </c>
@@ -18265,8 +18969,11 @@
         <v>29</v>
       </c>
       <c r="W236" s="2"/>
-    </row>
-    <row r="237" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X236" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="237" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A237">
         <v>237</v>
       </c>
@@ -18334,8 +19041,11 @@
         <v>29</v>
       </c>
       <c r="W237" s="2"/>
-    </row>
-    <row r="238" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X237" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="238" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A238">
         <v>238</v>
       </c>
@@ -18403,8 +19113,11 @@
         <v>29</v>
       </c>
       <c r="W238" s="2"/>
-    </row>
-    <row r="239" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X238" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="239" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A239">
         <v>239</v>
       </c>
@@ -18472,8 +19185,11 @@
         <v>29</v>
       </c>
       <c r="W239" s="2"/>
-    </row>
-    <row r="240" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X239" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="240" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A240">
         <v>240</v>
       </c>
@@ -18541,8 +19257,11 @@
         <v>29</v>
       </c>
       <c r="W240" s="2"/>
-    </row>
-    <row r="241" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X240" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="241" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A241">
         <v>241</v>
       </c>
@@ -18610,8 +19329,11 @@
         <v>29</v>
       </c>
       <c r="W241" s="2"/>
-    </row>
-    <row r="242" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X241" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="242" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A242">
         <v>242</v>
       </c>
@@ -18679,8 +19401,11 @@
         <v>29</v>
       </c>
       <c r="W242" s="2"/>
-    </row>
-    <row r="243" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X242" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="243" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A243">
         <v>243</v>
       </c>
@@ -18748,8 +19473,11 @@
         <v>29</v>
       </c>
       <c r="W243" s="2"/>
-    </row>
-    <row r="244" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X243" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="244" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A244">
         <v>244</v>
       </c>
@@ -18817,8 +19545,11 @@
         <v>29</v>
       </c>
       <c r="W244" s="2"/>
-    </row>
-    <row r="245" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X244" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="245" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A245">
         <v>245</v>
       </c>
@@ -18886,8 +19617,11 @@
         <v>29</v>
       </c>
       <c r="W245" s="2"/>
-    </row>
-    <row r="246" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X245" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="246" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A246">
         <v>246</v>
       </c>
@@ -18955,8 +19689,11 @@
         <v>29</v>
       </c>
       <c r="W246" s="2"/>
-    </row>
-    <row r="247" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X246" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="247" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A247">
         <v>247</v>
       </c>
@@ -19024,8 +19761,11 @@
         <v>29</v>
       </c>
       <c r="W247" s="2"/>
-    </row>
-    <row r="248" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X247" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="248" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A248">
         <v>248</v>
       </c>
@@ -19093,8 +19833,11 @@
         <v>29</v>
       </c>
       <c r="W248" s="2"/>
-    </row>
-    <row r="249" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X248" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="249" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A249">
         <v>249</v>
       </c>
@@ -19162,8 +19905,11 @@
         <v>29</v>
       </c>
       <c r="W249" s="2"/>
-    </row>
-    <row r="250" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X249" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="250" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A250">
         <v>250</v>
       </c>
@@ -19231,8 +19977,11 @@
         <v>29</v>
       </c>
       <c r="W250" s="2"/>
-    </row>
-    <row r="251" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X250" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="251" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A251">
         <v>251</v>
       </c>
@@ -19300,8 +20049,11 @@
         <v>29</v>
       </c>
       <c r="W251" s="2"/>
-    </row>
-    <row r="252" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X251" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="252" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A252">
         <v>252</v>
       </c>
@@ -19369,8 +20121,11 @@
         <v>29</v>
       </c>
       <c r="W252" s="2"/>
-    </row>
-    <row r="253" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X252" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="253" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A253">
         <v>253</v>
       </c>
@@ -19438,8 +20193,11 @@
         <v>29</v>
       </c>
       <c r="W253" s="2"/>
-    </row>
-    <row r="254" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X253" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="254" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A254">
         <v>254</v>
       </c>
@@ -19507,8 +20265,11 @@
         <v>29</v>
       </c>
       <c r="W254" s="2"/>
-    </row>
-    <row r="255" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X254" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="255" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A255">
         <v>255</v>
       </c>
@@ -19576,8 +20337,11 @@
         <v>29</v>
       </c>
       <c r="W255" s="2"/>
-    </row>
-    <row r="256" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X255" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="256" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A256">
         <v>256</v>
       </c>
@@ -19645,8 +20409,11 @@
         <v>29</v>
       </c>
       <c r="W256" s="2"/>
-    </row>
-    <row r="257" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X256" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="257" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A257">
         <v>257</v>
       </c>
@@ -19714,8 +20481,11 @@
         <v>29</v>
       </c>
       <c r="W257" s="2"/>
-    </row>
-    <row r="258" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X257" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="258" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A258">
         <v>258</v>
       </c>
@@ -19783,8 +20553,11 @@
         <v>29</v>
       </c>
       <c r="W258" s="2"/>
-    </row>
-    <row r="259" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X258" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="259" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A259">
         <v>259</v>
       </c>
@@ -19852,8 +20625,11 @@
         <v>29</v>
       </c>
       <c r="W259" s="2"/>
-    </row>
-    <row r="260" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X259" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="260" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A260">
         <v>260</v>
       </c>
@@ -19921,8 +20697,11 @@
         <v>29</v>
       </c>
       <c r="W260" s="2"/>
-    </row>
-    <row r="261" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X260" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="261" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A261">
         <v>261</v>
       </c>
@@ -19990,8 +20769,11 @@
         <v>29</v>
       </c>
       <c r="W261" s="2"/>
-    </row>
-    <row r="262" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X261" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="262" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A262">
         <v>262</v>
       </c>
@@ -20059,8 +20841,11 @@
         <v>29</v>
       </c>
       <c r="W262" s="2"/>
-    </row>
-    <row r="263" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X262" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="263" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A263">
         <v>263</v>
       </c>
@@ -20128,8 +20913,11 @@
         <v>29</v>
       </c>
       <c r="W263" s="2"/>
-    </row>
-    <row r="264" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X263" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="264" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A264">
         <v>264</v>
       </c>
@@ -20197,8 +20985,11 @@
         <v>29</v>
       </c>
       <c r="W264" s="2"/>
-    </row>
-    <row r="265" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X264" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="265" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A265">
         <v>265</v>
       </c>
@@ -20266,8 +21057,11 @@
         <v>29</v>
       </c>
       <c r="W265" s="2"/>
-    </row>
-    <row r="266" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X265" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="266" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A266">
         <v>266</v>
       </c>
@@ -20335,8 +21129,11 @@
         <v>29</v>
       </c>
       <c r="W266" s="2"/>
-    </row>
-    <row r="267" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X266" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="267" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A267">
         <v>267</v>
       </c>
@@ -20404,8 +21201,11 @@
         <v>29</v>
       </c>
       <c r="W267" s="2"/>
-    </row>
-    <row r="268" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X267" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="268" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A268">
         <v>268</v>
       </c>
@@ -20473,8 +21273,11 @@
         <v>29</v>
       </c>
       <c r="W268" s="2"/>
-    </row>
-    <row r="269" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X268" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="269" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A269">
         <v>269</v>
       </c>
@@ -20542,8 +21345,11 @@
         <v>29</v>
       </c>
       <c r="W269" s="2"/>
-    </row>
-    <row r="270" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X269" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="270" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A270">
         <v>270</v>
       </c>
@@ -20611,8 +21417,11 @@
         <v>29</v>
       </c>
       <c r="W270" s="2"/>
-    </row>
-    <row r="271" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X270" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="271" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A271">
         <v>271</v>
       </c>
@@ -20680,8 +21489,11 @@
         <v>29</v>
       </c>
       <c r="W271" s="2"/>
-    </row>
-    <row r="272" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X271" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="272" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A272">
         <v>272</v>
       </c>
@@ -20749,8 +21561,11 @@
         <v>29</v>
       </c>
       <c r="W272" s="2"/>
-    </row>
-    <row r="273" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X272" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="273" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A273">
         <v>273</v>
       </c>
@@ -20818,8 +21633,11 @@
         <v>29</v>
       </c>
       <c r="W273" s="2"/>
-    </row>
-    <row r="274" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X273" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="274" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A274">
         <v>274</v>
       </c>
@@ -20887,8 +21705,11 @@
         <v>29</v>
       </c>
       <c r="W274" s="2"/>
-    </row>
-    <row r="275" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X274" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="275" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A275">
         <v>275</v>
       </c>
@@ -20956,8 +21777,11 @@
         <v>29</v>
       </c>
       <c r="W275" s="2"/>
-    </row>
-    <row r="276" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X275" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="276" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A276">
         <v>276</v>
       </c>
@@ -21025,8 +21849,11 @@
         <v>29</v>
       </c>
       <c r="W276" s="2"/>
-    </row>
-    <row r="277" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X276" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="277" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A277">
         <v>277</v>
       </c>
@@ -21094,8 +21921,11 @@
         <v>29</v>
       </c>
       <c r="W277" s="2"/>
-    </row>
-    <row r="278" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X277" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="278" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A278">
         <v>278</v>
       </c>
@@ -21163,8 +21993,11 @@
         <v>29</v>
       </c>
       <c r="W278" s="2"/>
-    </row>
-    <row r="279" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X278" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="279" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A279">
         <v>279</v>
       </c>
@@ -21232,8 +22065,11 @@
         <v>29</v>
       </c>
       <c r="W279" s="2"/>
-    </row>
-    <row r="280" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X279" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="280" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A280">
         <v>280</v>
       </c>
@@ -21301,8 +22137,11 @@
         <v>29</v>
       </c>
       <c r="W280" s="2"/>
-    </row>
-    <row r="281" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X280" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="281" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A281">
         <v>281</v>
       </c>
@@ -21370,8 +22209,11 @@
         <v>29</v>
       </c>
       <c r="W281" s="2"/>
-    </row>
-    <row r="282" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X281" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="282" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A282">
         <v>282</v>
       </c>
@@ -21439,8 +22281,11 @@
         <v>29</v>
       </c>
       <c r="W282" s="2"/>
-    </row>
-    <row r="283" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X282" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="283" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A283">
         <v>283</v>
       </c>
@@ -21508,8 +22353,11 @@
         <v>29</v>
       </c>
       <c r="W283" s="2"/>
-    </row>
-    <row r="284" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X283" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="284" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A284">
         <v>284</v>
       </c>
@@ -21577,8 +22425,11 @@
         <v>29</v>
       </c>
       <c r="W284" s="2"/>
-    </row>
-    <row r="285" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X284" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="285" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A285">
         <v>285</v>
       </c>
@@ -21646,8 +22497,11 @@
         <v>29</v>
       </c>
       <c r="W285" s="2"/>
-    </row>
-    <row r="286" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X285" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="286" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A286">
         <v>286</v>
       </c>
@@ -21715,8 +22569,11 @@
         <v>29</v>
       </c>
       <c r="W286" s="8"/>
-    </row>
-    <row r="287" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X286" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="287" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A287">
         <v>287</v>
       </c>
@@ -21784,8 +22641,11 @@
         <v>29</v>
       </c>
       <c r="W287" s="8"/>
-    </row>
-    <row r="288" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X287" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="288" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A288">
         <v>288</v>
       </c>
@@ -21853,8 +22713,11 @@
         <v>29</v>
       </c>
       <c r="W288" s="8"/>
-    </row>
-    <row r="289" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X288" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="289" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A289">
         <v>289</v>
       </c>
@@ -21922,8 +22785,11 @@
         <v>29</v>
       </c>
       <c r="W289" s="8"/>
-    </row>
-    <row r="290" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X289" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="290" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A290">
         <v>290</v>
       </c>
@@ -21991,8 +22857,11 @@
         <v>29</v>
       </c>
       <c r="W290" s="8"/>
-    </row>
-    <row r="291" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X290" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="291" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A291">
         <v>291</v>
       </c>
@@ -22060,8 +22929,11 @@
         <v>29</v>
       </c>
       <c r="W291" s="8"/>
-    </row>
-    <row r="292" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X291" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="292" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A292">
         <v>292</v>
       </c>
@@ -22129,8 +23001,11 @@
         <v>29</v>
       </c>
       <c r="W292" s="8"/>
-    </row>
-    <row r="293" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X292" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="293" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A293">
         <v>293</v>
       </c>
@@ -22198,8 +23073,11 @@
         <v>29</v>
       </c>
       <c r="W293" s="8"/>
-    </row>
-    <row r="294" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X293" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="294" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A294">
         <v>294</v>
       </c>
@@ -22267,8 +23145,11 @@
         <v>29</v>
       </c>
       <c r="W294" s="8"/>
-    </row>
-    <row r="295" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X294" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="295" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A295">
         <v>295</v>
       </c>
@@ -22336,8 +23217,11 @@
         <v>29</v>
       </c>
       <c r="W295" s="8"/>
-    </row>
-    <row r="296" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X295" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="296" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A296">
         <v>296</v>
       </c>
@@ -22405,8 +23289,11 @@
         <v>29</v>
       </c>
       <c r="W296" s="8"/>
-    </row>
-    <row r="297" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X296" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="297" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A297">
         <v>297</v>
       </c>
@@ -22474,8 +23361,11 @@
         <v>29</v>
       </c>
       <c r="W297" s="8"/>
-    </row>
-    <row r="298" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X297" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="298" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A298">
         <v>298</v>
       </c>
@@ -22543,8 +23433,11 @@
         <v>29</v>
       </c>
       <c r="W298" s="8"/>
-    </row>
-    <row r="299" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X298" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="299" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A299">
         <v>299</v>
       </c>
@@ -22612,8 +23505,11 @@
         <v>29</v>
       </c>
       <c r="W299" s="8"/>
-    </row>
-    <row r="300" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X299" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="300" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A300">
         <v>300</v>
       </c>
@@ -22681,9 +23577,17 @@
         <v>29</v>
       </c>
       <c r="W300" s="8"/>
+      <c r="X300" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="301" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="X301" t="s">
+        <v>493</v>
+      </c>
     </row>
   </sheetData>
-  <dataValidations count="5">
+  <dataValidations count="6">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G136:G144 G146:G300 G2:G134" xr:uid="{58155949-CB1B-48D8-A226-133575A9F708}">
       <formula1>INDIRECT(D2 &amp; "_size")</formula1>
     </dataValidation>
@@ -22699,6 +23603,9 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C300" xr:uid="{C310BEFD-AB98-4273-AFFC-E63848748976}">
       <formula1>Category</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2:X301" xr:uid="{653C3170-9DF8-42FB-AE2C-33FFA3FB8F23}">
+      <formula1>"LandLord , B&amp;Z "</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -22707,23 +23614,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AFFF102-26E2-4B46-85F9-06F0C3E86F0F}">
   <dimension ref="A1:X86"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.42578125" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" customWidth="1"/>
-    <col min="4" max="4" width="23.7109375" customWidth="1"/>
-    <col min="5" max="5" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.44140625" customWidth="1"/>
+    <col min="3" max="3" width="15.88671875" customWidth="1"/>
+    <col min="4" max="4" width="23.6640625" customWidth="1"/>
+    <col min="5" max="5" width="28.88671875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="33.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.42578125" customWidth="1"/>
-    <col min="10" max="10" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="23.5703125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="33.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.44140625" customWidth="1"/>
+    <col min="10" max="10" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="23.5546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="10.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -22793,8 +23701,11 @@
       <c r="W1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X1" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B2" s="4" t="s">
         <v>28</v>
       </c>
@@ -22858,8 +23769,11 @@
       <c r="V2" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X2" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
         <v>278</v>
       </c>
@@ -22924,8 +23838,11 @@
         <v>147</v>
       </c>
       <c r="W3" s="2"/>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X3" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
         <v>28</v>
       </c>
@@ -22990,8 +23907,11 @@
         <v>29</v>
       </c>
       <c r="W4" s="2"/>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X4" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>28</v>
       </c>
@@ -23054,8 +23974,11 @@
         <v>29</v>
       </c>
       <c r="W5" s="2"/>
-    </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X5" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
         <v>28</v>
       </c>
@@ -23118,8 +24041,11 @@
         <v>29</v>
       </c>
       <c r="W6" s="2"/>
-    </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X6" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
         <v>28</v>
       </c>
@@ -23184,8 +24110,11 @@
         <v>29</v>
       </c>
       <c r="W7" s="2"/>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X7" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
         <v>28</v>
       </c>
@@ -23250,8 +24179,11 @@
         <v>29</v>
       </c>
       <c r="W8" s="2"/>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X8" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
         <v>28</v>
       </c>
@@ -23313,8 +24245,11 @@
         <v>29</v>
       </c>
       <c r="W9" s="2"/>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X9" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
         <v>28</v>
       </c>
@@ -23379,8 +24314,11 @@
         <v>29</v>
       </c>
       <c r="W10" s="2"/>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X10" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
         <v>28</v>
       </c>
@@ -23445,8 +24383,11 @@
         <v>147</v>
       </c>
       <c r="W11" s="2"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X11" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
         <v>28</v>
       </c>
@@ -23508,8 +24449,11 @@
         <v>29</v>
       </c>
       <c r="W12" s="2"/>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X12" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
         <v>296</v>
       </c>
@@ -23574,8 +24518,11 @@
         <v>29</v>
       </c>
       <c r="W13" s="2"/>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X13" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
         <v>297</v>
       </c>
@@ -23640,8 +24587,11 @@
         <v>29</v>
       </c>
       <c r="W14" s="2"/>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X14" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
         <v>28</v>
       </c>
@@ -23703,8 +24653,11 @@
       <c r="V15" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X15" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
         <v>28</v>
       </c>
@@ -23769,8 +24722,11 @@
         <v>29</v>
       </c>
       <c r="W16" s="2"/>
-    </row>
-    <row r="17" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="X16" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="17" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
         <v>28</v>
       </c>
@@ -23832,8 +24788,11 @@
         <v>29</v>
       </c>
       <c r="W17" s="2"/>
-    </row>
-    <row r="18" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="X17" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="18" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
         <v>28</v>
       </c>
@@ -23898,8 +24857,11 @@
         <v>29</v>
       </c>
       <c r="W18" s="2"/>
-    </row>
-    <row r="19" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="X18" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="19" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
         <v>28</v>
       </c>
@@ -23962,8 +24924,11 @@
         <v>29</v>
       </c>
       <c r="W19" s="2"/>
-    </row>
-    <row r="20" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="X19" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="20" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
         <v>303</v>
       </c>
@@ -24028,8 +24993,11 @@
         <v>29</v>
       </c>
       <c r="W20" s="2"/>
-    </row>
-    <row r="21" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="X20" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="21" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
         <v>305</v>
       </c>
@@ -24094,8 +25062,11 @@
         <v>29</v>
       </c>
       <c r="W21" s="2"/>
-    </row>
-    <row r="22" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="X21" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="22" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B22" s="4" t="s">
         <v>28</v>
       </c>
@@ -24160,8 +25131,11 @@
         <v>29</v>
       </c>
       <c r="W22" s="2"/>
-    </row>
-    <row r="23" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="X22" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="23" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
         <v>313</v>
       </c>
@@ -24226,8 +25200,11 @@
         <v>29</v>
       </c>
       <c r="W23" s="2"/>
-    </row>
-    <row r="24" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="X23" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="24" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
         <v>313</v>
       </c>
@@ -24292,8 +25269,11 @@
         <v>29</v>
       </c>
       <c r="W24" s="2"/>
-    </row>
-    <row r="25" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="X24" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="25" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
         <v>316</v>
       </c>
@@ -24358,8 +25338,11 @@
         <v>29</v>
       </c>
       <c r="W25" s="2"/>
-    </row>
-    <row r="26" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="X25" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="26" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
         <v>28</v>
       </c>
@@ -24424,8 +25407,11 @@
         <v>29</v>
       </c>
       <c r="W26" s="2"/>
-    </row>
-    <row r="27" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="X26" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="27" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
         <v>317</v>
       </c>
@@ -24490,8 +25476,11 @@
         <v>29</v>
       </c>
       <c r="W27" s="2"/>
-    </row>
-    <row r="28" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="X27" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="28" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
         <v>319</v>
       </c>
@@ -24556,9 +25545,11 @@
         <v>29</v>
       </c>
       <c r="W28" s="2"/>
-      <c r="X28" s="2"/>
-    </row>
-    <row r="29" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="X28" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="29" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B29" s="4" t="s">
         <v>28</v>
       </c>
@@ -24621,8 +25612,11 @@
         <v>29</v>
       </c>
       <c r="W29" s="2"/>
-    </row>
-    <row r="30" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="X29" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="30" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B30" s="4" t="s">
         <v>28</v>
       </c>
@@ -24685,8 +25679,11 @@
         <v>29</v>
       </c>
       <c r="W30" s="2"/>
-    </row>
-    <row r="31" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="X30" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="31" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B31" s="4" t="s">
         <v>323</v>
       </c>
@@ -24751,8 +25748,11 @@
         <v>29</v>
       </c>
       <c r="W31" s="2"/>
-    </row>
-    <row r="32" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="X31" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="32" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B32" s="4" t="s">
         <v>326</v>
       </c>
@@ -24817,8 +25817,11 @@
         <v>29</v>
       </c>
       <c r="W32" s="2"/>
-    </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X32" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B33" s="4" t="s">
         <v>328</v>
       </c>
@@ -24880,8 +25883,11 @@
         <v>29</v>
       </c>
       <c r="W33" s="2"/>
-    </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X33" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="34" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B34" s="4" t="s">
         <v>330</v>
       </c>
@@ -24946,8 +25952,11 @@
         <v>29</v>
       </c>
       <c r="W34" s="14"/>
-    </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X34" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="35" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B35" s="4" t="s">
         <v>28</v>
       </c>
@@ -25012,8 +26021,11 @@
         <v>29</v>
       </c>
       <c r="W35" s="2"/>
-    </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X35" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="36" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B36" s="4" t="s">
         <v>28</v>
       </c>
@@ -25078,8 +26090,11 @@
         <v>29</v>
       </c>
       <c r="W36" s="2"/>
-    </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X36" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="37" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>168</v>
       </c>
@@ -25147,8 +26162,11 @@
         <v>29</v>
       </c>
       <c r="W37" s="2"/>
-    </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X37" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="38" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>180</v>
       </c>
@@ -25214,8 +26232,11 @@
         <v>29</v>
       </c>
       <c r="W38" s="2"/>
-    </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X38" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="39" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>186</v>
       </c>
@@ -25283,8 +26304,11 @@
         <v>29</v>
       </c>
       <c r="W39" s="2"/>
-    </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X39" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="40" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>187</v>
       </c>
@@ -25350,8 +26374,11 @@
         <v>29</v>
       </c>
       <c r="W40" s="2"/>
-    </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X40" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="41" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>188</v>
       </c>
@@ -25416,8 +26443,11 @@
         <v>29</v>
       </c>
       <c r="W41" s="2"/>
-    </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X41" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="42" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>189</v>
       </c>
@@ -25485,8 +26515,11 @@
         <v>29</v>
       </c>
       <c r="W42" s="2"/>
-    </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X42" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="43" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>196</v>
       </c>
@@ -25549,8 +26582,11 @@
         <v>29</v>
       </c>
       <c r="W43" s="2"/>
-    </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X43" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="44" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>197</v>
       </c>
@@ -25613,8 +26649,11 @@
         <v>29</v>
       </c>
       <c r="W44" s="2"/>
-    </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X44" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="45" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>207</v>
       </c>
@@ -25682,8 +26721,11 @@
         <v>29</v>
       </c>
       <c r="W45" s="2"/>
-    </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X45" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="46" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>208</v>
       </c>
@@ -25749,8 +26791,11 @@
         <v>29</v>
       </c>
       <c r="W46" s="2"/>
-    </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X46" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="47" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>209</v>
       </c>
@@ -25816,8 +26861,11 @@
         <v>29</v>
       </c>
       <c r="W47" s="2"/>
-    </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X47" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="48" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>210</v>
       </c>
@@ -25877,8 +26925,11 @@
         <v>29</v>
       </c>
       <c r="W48" s="2"/>
-    </row>
-    <row r="49" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X48" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="49" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>240</v>
       </c>
@@ -25941,8 +26992,11 @@
       <c r="V49" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="50" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X49" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="50" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>264</v>
       </c>
@@ -26010,8 +27064,11 @@
         <v>29</v>
       </c>
       <c r="W50" s="2"/>
-    </row>
-    <row r="51" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X50" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="51" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>265</v>
       </c>
@@ -26079,8 +27136,11 @@
         <v>29</v>
       </c>
       <c r="W51" s="2"/>
-    </row>
-    <row r="52" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X51" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="52" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>267</v>
       </c>
@@ -26148,8 +27208,11 @@
         <v>29</v>
       </c>
       <c r="W52" s="2"/>
-    </row>
-    <row r="53" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X52" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="53" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>268</v>
       </c>
@@ -26217,8 +27280,11 @@
         <v>29</v>
       </c>
       <c r="W53" s="2"/>
-    </row>
-    <row r="54" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X53" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="54" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B54" t="s">
         <v>28</v>
       </c>
@@ -26283,8 +27349,11 @@
         <v>29</v>
       </c>
       <c r="W54" s="2"/>
-    </row>
-    <row r="55" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X54" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="55" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>283</v>
       </c>
@@ -26352,8 +27421,11 @@
         <v>29</v>
       </c>
       <c r="W55" s="2"/>
-    </row>
-    <row r="56" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X55" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="56" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>296</v>
       </c>
@@ -26421,8 +27493,11 @@
         <v>29</v>
       </c>
       <c r="W56" s="2"/>
-    </row>
-    <row r="57" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X56" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="57" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>297</v>
       </c>
@@ -26490,8 +27565,11 @@
         <v>29</v>
       </c>
       <c r="W57" s="2"/>
-    </row>
-    <row r="58" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X57" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="58" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B58" t="s">
         <v>28</v>
       </c>
@@ -26556,8 +27634,11 @@
         <v>29</v>
       </c>
       <c r="W58" s="2"/>
-    </row>
-    <row r="59" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X58" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="59" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B59" t="s">
         <v>362</v>
       </c>
@@ -26622,8 +27703,11 @@
         <v>29</v>
       </c>
       <c r="W59" s="2"/>
-    </row>
-    <row r="60" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X59" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="60" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B60" t="s">
         <v>364</v>
       </c>
@@ -26688,8 +27772,11 @@
         <v>29</v>
       </c>
       <c r="W60" s="2"/>
-    </row>
-    <row r="61" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X60" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="61" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B61" t="s">
         <v>366</v>
       </c>
@@ -26751,8 +27838,11 @@
         <v>29</v>
       </c>
       <c r="W61" s="2"/>
-    </row>
-    <row r="62" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X61" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="62" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B62" t="s">
         <v>28</v>
       </c>
@@ -26817,8 +27907,11 @@
         <v>29</v>
       </c>
       <c r="W62" s="2"/>
-    </row>
-    <row r="63" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X62" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="63" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B63" t="s">
         <v>28</v>
       </c>
@@ -26881,8 +27974,11 @@
         <v>29</v>
       </c>
       <c r="W63" s="2"/>
-    </row>
-    <row r="64" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X63" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="64" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B64" t="s">
         <v>28</v>
       </c>
@@ -26945,8 +28041,11 @@
         <v>29</v>
       </c>
       <c r="W64" s="2"/>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X64" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B65" t="s">
         <v>28</v>
       </c>
@@ -27011,8 +28110,11 @@
         <v>29</v>
       </c>
       <c r="W65" s="2"/>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X65" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B66" t="s">
         <v>28</v>
       </c>
@@ -27077,8 +28179,11 @@
         <v>29</v>
       </c>
       <c r="W66" s="2"/>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X66" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B67" t="s">
         <v>28</v>
       </c>
@@ -27143,8 +28248,11 @@
         <v>29</v>
       </c>
       <c r="W67" s="2"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X67" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B68" t="s">
         <v>28</v>
       </c>
@@ -27206,8 +28314,11 @@
         <v>29</v>
       </c>
       <c r="W68" s="2"/>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X68" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B69" t="s">
         <v>371</v>
       </c>
@@ -27272,8 +28383,11 @@
         <v>29</v>
       </c>
       <c r="W69" s="2"/>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X69" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B70" t="s">
         <v>373</v>
       </c>
@@ -27338,8 +28452,11 @@
         <v>29</v>
       </c>
       <c r="W70" s="2"/>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X70" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B71" t="s">
         <v>375</v>
       </c>
@@ -27401,8 +28518,11 @@
         <v>29</v>
       </c>
       <c r="W71" s="2"/>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X71" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B72" s="22">
         <v>2116885520056</v>
       </c>
@@ -27467,8 +28587,11 @@
         <v>29</v>
       </c>
       <c r="W72" s="2"/>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X72" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B73" t="s">
         <v>28</v>
       </c>
@@ -27533,8 +28656,11 @@
         <v>29</v>
       </c>
       <c r="W73" s="2"/>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X73" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B74" t="s">
         <v>28</v>
       </c>
@@ -27599,8 +28725,11 @@
         <v>29</v>
       </c>
       <c r="W74" s="2"/>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X74" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B75" t="s">
         <v>379</v>
       </c>
@@ -27665,8 +28794,11 @@
         <v>29</v>
       </c>
       <c r="W75" s="2"/>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X75" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B76" t="s">
         <v>28</v>
       </c>
@@ -27731,8 +28863,11 @@
         <v>29</v>
       </c>
       <c r="W76" s="2"/>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X76" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B77" t="s">
         <v>28</v>
       </c>
@@ -27797,8 +28932,11 @@
         <v>29</v>
       </c>
       <c r="W77" s="2"/>
-    </row>
-    <row r="78" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X77" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="78" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B78" t="s">
         <v>381</v>
       </c>
@@ -27863,8 +29001,11 @@
         <v>29</v>
       </c>
       <c r="W78" s="2"/>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X78" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B79" t="s">
         <v>28</v>
       </c>
@@ -27929,8 +29070,11 @@
         <v>29</v>
       </c>
       <c r="W79" s="2"/>
-    </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X79" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="80" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B80" t="s">
         <v>383</v>
       </c>
@@ -27995,8 +29139,11 @@
         <v>29</v>
       </c>
       <c r="W80" s="2"/>
-    </row>
-    <row r="81" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X80" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="81" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B81" s="23" t="s">
         <v>28</v>
       </c>
@@ -28056,8 +29203,11 @@
       <c r="V81" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="82" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X81" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="82" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B82" t="s">
         <v>28</v>
       </c>
@@ -28122,8 +29272,11 @@
         <v>29</v>
       </c>
       <c r="W82" s="8"/>
-    </row>
-    <row r="83" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X82" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="83" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B83" t="s">
         <v>28</v>
       </c>
@@ -28188,8 +29341,11 @@
         <v>29</v>
       </c>
       <c r="W83" s="8"/>
-    </row>
-    <row r="84" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X83" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="84" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B84" t="s">
         <v>386</v>
       </c>
@@ -28248,8 +29404,11 @@
       <c r="V84" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="85" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X84" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="85" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B85" t="s">
         <v>392</v>
       </c>
@@ -28310,8 +29469,11 @@
       <c r="V85" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="86" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X85" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="86" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B86" t="s">
         <v>28</v>
       </c>
@@ -28375,10 +29537,13 @@
       <c r="V86" s="2" t="s">
         <v>29</v>
       </c>
+      <c r="X86" s="2" t="s">
+        <v>493</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:W86" xr:uid="{7AFFF102-26E2-4B46-85F9-06F0C3E86F0F}"/>
-  <dataValidations count="4">
+  <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F86 G49" xr:uid="{EFD74BD8-58C9-4ACB-93B3-5302AF9CB479}">
       <formula1>INDIRECT(D2&amp;"_material")</formula1>
     </dataValidation>
@@ -28391,6 +29556,9 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G48 G50:G86" xr:uid="{4875B19E-87F5-497F-BC8F-1473FB197838}">
       <formula1>INDIRECT(D2 &amp; "_size")</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2:X86" xr:uid="{FB1E39CC-736C-412E-AC97-78C1F456E3B3}">
+      <formula1>"LandLord , B&amp;Z "</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -28400,23 +29568,23 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{087FDD54-5E17-401C-A88E-55822B904567}">
   <dimension ref="A1:X7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.6640625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -28486,8 +29654,11 @@
       <c r="W1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="2" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="X1" s="1" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B2" s="12" t="s">
         <v>28</v>
       </c>
@@ -28549,8 +29720,11 @@
         <v>29</v>
       </c>
       <c r="W2" s="14"/>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="X2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
         <v>28</v>
       </c>
@@ -28612,9 +29786,11 @@
         <v>29</v>
       </c>
       <c r="W3" s="2"/>
-      <c r="X3" s="24"/>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="X3" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
         <v>28</v>
       </c>
@@ -28676,8 +29852,11 @@
         <v>29</v>
       </c>
       <c r="W4" s="2"/>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="X4" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>249</v>
       </c>
@@ -28708,7 +29887,7 @@
       <c r="J5" s="8" t="s">
         <v>402</v>
       </c>
-      <c r="K5" s="25" t="s">
+      <c r="K5" s="24" t="s">
         <v>403</v>
       </c>
       <c r="L5" s="14" t="s">
@@ -28745,8 +29924,11 @@
         <v>147</v>
       </c>
       <c r="W5" s="2"/>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="X5" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>251</v>
       </c>
@@ -28811,8 +29993,11 @@
         <v>29</v>
       </c>
       <c r="W6" s="2"/>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="X6" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>254</v>
       </c>
@@ -28880,9 +30065,12 @@
         <v>29</v>
       </c>
       <c r="W7" s="2"/>
+      <c r="X7" t="s">
+        <v>493</v>
+      </c>
     </row>
   </sheetData>
-  <dataValidations count="4">
+  <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F7" xr:uid="{049F1F64-FDBE-45B5-B292-C2C5EC3F1001}">
       <formula1>INDIRECT(D2&amp;"_material")</formula1>
     </dataValidation>
@@ -28895,6 +30083,9 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G7" xr:uid="{A54186C2-8BD9-4A1F-9A77-54DD56F0EC69}">
       <formula1>INDIRECT(D2 &amp; "_size")</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2:X8" xr:uid="{3A23A9C1-FC99-411F-BEC7-2CF88E51B481}">
+      <formula1>"LandLord , B&amp;Z "</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -28902,17 +30093,17 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45841932-2100-4D5F-A69E-818128AA5E3E}">
-  <dimension ref="A1:AA4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AB4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.109375" customWidth="1"/>
+    <col min="4" max="4" width="12.5546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -28994,8 +30185,11 @@
       <c r="AA1" s="1" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AB1" s="1" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -29072,8 +30266,11 @@
         <f>#REF!&amp; ", " &amp;#REF!&amp;", "&amp; C2</f>
         <v>#REF!</v>
       </c>
-    </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AB2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -29110,7 +30307,7 @@
       <c r="N3" t="s">
         <v>419</v>
       </c>
-      <c r="O3" s="26">
+      <c r="O3" s="25">
         <v>45689</v>
       </c>
       <c r="P3" t="s">
@@ -29143,8 +30340,11 @@
       <c r="Z3" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AB3" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -29217,9 +30417,12 @@
       <c r="Z4" t="s">
         <v>23</v>
       </c>
+      <c r="AB4" t="s">
+        <v>493</v>
+      </c>
     </row>
   </sheetData>
-  <dataValidations count="5">
+  <dataValidations count="6">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J4" xr:uid="{FF67C21E-F325-4BB0-9F09-F8762B00673B}">
       <formula1>INDIRECT(D2 &amp; "_load")</formula1>
     </dataValidation>
@@ -29235,6 +30438,9 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E4" xr:uid="{A6866A63-7F58-4016-A85A-E64696944467}">
       <formula1>INDIRECT(D2 &amp; "_categories")</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB2:AB4" xr:uid="{8FE0B5E4-A8C3-4187-836F-3C6167F310FC}">
+      <formula1>"LandLord , B&amp;Z "</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -29243,19 +30449,19 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E46FE8D-6B9D-4019-AD13-4A9515E01ECE}">
   <dimension ref="A1:AG35"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="30.28515625" customWidth="1"/>
-    <col min="16" max="16" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.33203125" customWidth="1"/>
+    <col min="16" max="16" width="19.44140625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="55" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="28.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -29319,8 +30525,11 @@
       <c r="U1" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="V1" s="1" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="2" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -29384,8 +30593,11 @@
       <c r="U2" t="s">
         <v>427</v>
       </c>
-    </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="V2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -29447,8 +30659,11 @@
       <c r="U3" t="s">
         <v>429</v>
       </c>
-    </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="V3" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -29510,8 +30725,11 @@
       <c r="U4" t="s">
         <v>438</v>
       </c>
-    </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="V4" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -29573,8 +30791,11 @@
       <c r="U5" t="s">
         <v>440</v>
       </c>
-    </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="V5" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="6" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -29636,8 +30857,11 @@
       <c r="U6" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="V6" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="7" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -29699,8 +30923,11 @@
       <c r="U7" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="V7" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -29762,8 +30989,11 @@
       <c r="U8" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="V8" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -29824,8 +31054,11 @@
       <c r="U9" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="V9" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -29884,8 +31117,11 @@
       <c r="U10" t="s">
         <v>450</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="V10" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -29949,8 +31185,11 @@
       <c r="U11" t="s">
         <v>427</v>
       </c>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="V11" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -30014,8 +31253,11 @@
       <c r="U12" t="s">
         <v>453</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="V12" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -30077,8 +31319,11 @@
       <c r="U13" t="s">
         <v>438</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="V13" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -30140,6 +31385,9 @@
       <c r="U14" t="str">
         <f t="shared" ref="U14:U35" si="0" xml:space="preserve"> E14&amp;", " &amp; D14 &amp;", " &amp;H14</f>
         <v xml:space="preserve">Large UPS, UPS, </v>
+      </c>
+      <c r="V14" t="s">
+        <v>493</v>
       </c>
       <c r="AA14" s="1"/>
       <c r="AB14" s="1"/>
@@ -30149,11 +31397,11 @@
       <c r="AF14" s="1"/>
       <c r="AG14" s="1"/>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" s="27" t="s">
+      <c r="B15" s="26" t="s">
         <v>458</v>
       </c>
       <c r="C15" t="s">
@@ -30212,12 +31460,15 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">Server, Server, </v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="V15" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" s="27" t="s">
+      <c r="B16" s="26" t="s">
         <v>460</v>
       </c>
       <c r="C16" t="s">
@@ -30276,8 +31527,11 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">Server, Server, </v>
       </c>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V16" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -30339,8 +31593,11 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">Indoor Cameras, Camera, </v>
       </c>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V17" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -30402,8 +31659,11 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">Indoor Cameras, Camera, </v>
       </c>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V18" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -30465,8 +31725,11 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">Server, Server, </v>
       </c>
-    </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V19" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -30531,8 +31794,11 @@
         <f t="shared" si="0"/>
         <v>colored Printer, Printer, HP</v>
       </c>
-    </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V20" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -30597,8 +31863,11 @@
         <f t="shared" si="0"/>
         <v>Router, Router, TP-Link</v>
       </c>
-    </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V21" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -30663,8 +31932,11 @@
         <f t="shared" si="0"/>
         <v>colored Printer, Printer, HP</v>
       </c>
-    </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V22" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -30726,8 +31998,11 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">Indoor Cameras, Camera, </v>
       </c>
-    </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V23" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -30789,8 +32064,11 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">Indoor Cameras, Camera, </v>
       </c>
-    </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V24" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -30855,8 +32133,11 @@
         <f t="shared" si="0"/>
         <v>colored Printer, printer, hp</v>
       </c>
-    </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V25" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -30919,8 +32200,11 @@
         <f t="shared" si="0"/>
         <v>colored Printer, Printer, Xerox</v>
       </c>
-    </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V26" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
@@ -30985,8 +32269,11 @@
         <f t="shared" si="0"/>
         <v>wireless keyboard, Keyboard, Apple</v>
       </c>
-    </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V27" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -31051,8 +32338,11 @@
         <f t="shared" si="0"/>
         <v>Large UPS, UPS, Xerox</v>
       </c>
-    </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V28" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -31117,8 +32407,11 @@
         <f t="shared" si="0"/>
         <v>wired keyboard, Keyboard, Logitech</v>
       </c>
-    </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V29" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
@@ -31183,8 +32476,11 @@
         <f t="shared" si="0"/>
         <v>colored Printer, Printer, Xerox</v>
       </c>
-    </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V30" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
@@ -31246,8 +32542,11 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">Indoor Cameras, Camera, </v>
       </c>
-    </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V31" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
@@ -31303,8 +32602,11 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">Indoor Cameras, Camera, </v>
       </c>
-    </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V32" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
@@ -31367,8 +32669,11 @@
         <f t="shared" si="0"/>
         <v>colored Printer, Printer, Xerox</v>
       </c>
-    </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V33" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
@@ -31433,8 +32738,11 @@
         <f t="shared" si="0"/>
         <v>colored Printer, Printer, HP</v>
       </c>
-    </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V34" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
@@ -31459,7 +32767,7 @@
       <c r="I35" t="s">
         <v>28</v>
       </c>
-      <c r="J35" s="28">
+      <c r="J35" s="27">
         <v>600</v>
       </c>
       <c r="K35" t="s">
@@ -31496,9 +32804,12 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">Inverter, Inverter, </v>
       </c>
+      <c r="V35" t="s">
+        <v>493</v>
+      </c>
     </row>
   </sheetData>
-  <dataValidations count="4">
+  <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D35" xr:uid="{3AEEB505-4466-444E-ACF7-37EFA975ACF9}">
       <formula1>INDIRECT(C2 &amp; "_category")</formula1>
     </dataValidation>
@@ -31511,6 +32822,9 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F5 F9:F35" xr:uid="{562E144E-2576-46E1-B76C-317B450EC952}">
       <formula1>INDIRECT(D2 &amp; "_size")</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V35" xr:uid="{59A9150C-F028-4FD7-A511-C638E4099751}">
+      <formula1>"LandLord , B&amp;Z "</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -31519,14 +32833,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB899B9E-9D29-4608-AC57-3843A909BED5}">
   <dimension ref="A1:T1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.5703125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="3" max="3" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.5546875" customWidth="1"/>
+    <col min="5" max="5" width="10.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -31596,15 +32910,15 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31D0FD15-6627-45B8-AE32-055E4B703EE2}">
   <dimension ref="A1:T1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.7109375" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
